--- a/POSICAO_DE_ESTOQUE/MARÇO_2026.xlsx
+++ b/POSICAO_DE_ESTOQUE/MARÇO_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Comercial\Desktop\Dre\POSIÇÃO DE ESTOQUE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5582F2E-2C63-46A9-B83D-92577013E85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F910601F-891D-4714-A96B-5B53098DFD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0A61FA85-5004-43FF-98AE-E90C80947248}"/>
   </bookViews>
@@ -79,13 +79,11 @@
       <sz val="8"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="6"/>
       <color indexed="8"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -138,26 +136,26 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -487,61 +485,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="12" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5" ht="12" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6">
-        <v>30156</v>
-      </c>
-      <c r="C2" s="6">
-        <v>40.287741272239003</v>
-      </c>
-      <c r="D2" s="7">
-        <v>507531.90840000001</v>
-      </c>
-      <c r="E2" s="4"/>
+      <c r="B2" s="5">
+        <v>30065</v>
+      </c>
+      <c r="C2" s="5">
+        <v>40.295192759952968</v>
+      </c>
+      <c r="D2" s="6">
+        <v>506497.62359999999</v>
+      </c>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6">
-        <v>1462203274</v>
-      </c>
-      <c r="C3" s="6">
-        <v>43.134266023590563</v>
-      </c>
-      <c r="D3" s="7">
-        <v>21903875524.070702</v>
+      <c r="B3" s="5">
+        <v>80910</v>
+      </c>
+      <c r="C3" s="5">
+        <v>43.173704856313208</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1287077.0841000001</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="8">
-        <v>1462233430</v>
+        <v>110975</v>
       </c>
       <c r="C4" s="8">
-        <v>41.711003647914779</v>
+        <v>41.734448808133088</v>
       </c>
       <c r="D4" s="8">
-        <v>21904383055.979099</v>
+        <v>1793574.7076999999</v>
       </c>
     </row>
   </sheetData>
